--- a/data/trans_orig/RUIDO_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>31840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59850</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60318</t>
+          <t>60031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75328</t>
+          <t>75529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49742</t>
+          <t>49836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96291</t>
+          <t>97184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124882</t>
+          <t>124540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43038</t>
+          <t>42145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>24643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22875</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>41570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31258</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45651</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25145</t>
+          <t>25433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35452</t>
+          <t>35276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29492</t>
+          <t>29588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38843</t>
+          <t>39251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48060</t>
+          <t>48058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>45266</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39361</t>
+          <t>40156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55882</t>
+          <t>56722</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77073</t>
+          <t>77336</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98247</t>
+          <t>98195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11188</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22729</t>
+          <t>23142</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40283</t>
+          <t>39488</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37850</t>
+          <t>37902</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59024</t>
+          <t>58761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43171</t>
+          <t>42459</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53235</t>
+          <t>52996</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74493</t>
+          <t>75157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82613</t>
+          <t>82492</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>120377</t>
+          <t>121259</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133408</t>
+          <t>133626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15748</t>
+          <t>16460</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>240776</t>
+          <t>242664</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>274374</t>
+          <t>275054</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>268712</t>
+          <t>268513</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>303539</t>
+          <t>303444</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>523082</t>
+          <t>519201</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>570088</t>
+          <t>569331</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>57169</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>88879</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82610</t>
+          <t>82705</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117437</t>
+          <t>117636</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>147603</t>
+          <t>148360</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>194609</t>
+          <t>198490</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_1_R-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24721</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31102</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28963</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24878</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31840</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70940</t>
+          <t>56701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4409</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5237</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9322</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15,31%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38316</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27443</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>44823</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>70,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>50,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>68889</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>60031</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>75529</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>37401</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>46530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>111450</t>
+          <t>80811</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>97184</t>
+          <t>68823</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124540</t>
+          <t>88941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>83,5%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16199</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9692</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27072</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,78%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9459</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2819</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18317</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28928</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>27879</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14789</t>
+          <t>17570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42145</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23312</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19793</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25667</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>83,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>70,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21024</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16468</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24643</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>71,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29006</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>47300</t>
+          <t>44323</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41570</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52187</t>
+          <t>48411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4611</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2256</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8130</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8429</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4810</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12985</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28,62%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>4541</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8693</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19310</t>
+          <t>17450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15440</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9763</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20172</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17680</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26456</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>89,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20980</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31383</t>
+          <t>30391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44931</t>
+          <t>44649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9748</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15425</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>61,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3027</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11803</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>17042</t>
+          <t>16970</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11845</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8107</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16294</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8639</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5627</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12169</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>25938</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>15698</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11249</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>19436</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>56,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>15223</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11693</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18235</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>76,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19174</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>30585</t>
+          <t>31498</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25433</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35276</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>23045</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>18873</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>25785</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>79,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>64,7%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>88,39%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>14539</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19759</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>69,82%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26231</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29588</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>44139</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39251</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48058</t>
+          <t>44647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6125</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3385</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10297</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>11,61%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>35,3%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>45597</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>37876</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>53272</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>61,14%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>50,79%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>71,43%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>39753</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>33312</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>45266</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>70,42%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>59,01%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>80,18%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>48614</t>
+          <t>37518</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>30296</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56722</t>
+          <t>42599</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>88366</t>
+          <t>83116</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>77336</t>
+          <t>73969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98195</t>
+          <t>92859</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>28980</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>21305</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>36701</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>38,86%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>28,57%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>49,21%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>16701</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>11188</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>23142</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>29,58%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>17574</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39488</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>47731</t>
+          <t>46554</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>36811</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58761</t>
+          <t>55701</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,96%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>55092</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>55092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>55092</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>80443</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>74852</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>83528</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>97,1%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>48943</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>42459</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>52996</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>83,07%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>72,06%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>89,95%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>79549</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75157</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82492</t>
+          <t>54447</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>128493</t>
+          <t>130561</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121259</t>
+          <t>122920</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>133626</t>
+          <t>136366</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2497</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>11173</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>9976</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>5923</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>16460</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>266611</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>249873</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>282316</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>78,87%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>351</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>256677</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>242664</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>275054</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>77,42%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>73,19%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>82,96%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>288294</t>
+          <t>224681</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>268513</t>
+          <t>211785</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>303444</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>544970</t>
+          <t>491292</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>519201</t>
+          <t>469918</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>569331</t>
+          <t>509658</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>91354</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>75649</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>108092</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>25,52%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>21,13%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>74866</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>56489</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>88879</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>97855</t>
+          <t>76088</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>82705</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117636</t>
+          <t>88984</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>172721</t>
+          <t>167441</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>148360</t>
+          <t>149075</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>198490</t>
+          <t>188815</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
